--- a/data_lake/descensos_temperatura/dt=2026-08-01/excel/PronosticoMunicipal_DescensosTemperatura_72h.xlsx
+++ b/data_lake/descensos_temperatura/dt=2026-08-01/excel/PronosticoMunicipal_DescensosTemperatura_72h.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K283"/>
+  <dimension ref="A1:K258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,17 +488,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -541,17 +541,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -594,17 +594,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -647,17 +647,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -700,17 +700,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -753,17 +753,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -806,17 +806,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -859,17 +859,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -912,17 +912,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -965,17 +965,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1071,17 +1071,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1230,17 +1230,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1283,17 +1283,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1389,17 +1389,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1495,17 +1495,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1548,17 +1548,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1580,11 +1580,11 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -1601,17 +1601,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1633,11 +1633,11 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -1654,17 +1654,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1739,11 +1739,11 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -1760,17 +1760,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1845,11 +1845,11 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -1866,17 +1866,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1898,11 +1898,11 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -1919,17 +1919,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1951,11 +1951,11 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -2004,11 +2004,11 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -2025,17 +2025,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -2078,17 +2078,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -2184,17 +2184,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -2216,11 +2216,11 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -2237,17 +2237,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2290,17 +2290,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2343,17 +2343,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2449,17 +2449,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -2555,17 +2555,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -2573,25 +2573,25 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>50223</t>
+          <t>76111</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Cubarral</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Valle del Cauca</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -2608,17 +2608,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -2626,25 +2626,25 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>25120</t>
+          <t>50223</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Cubarral</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -2661,17 +2661,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -2679,17 +2679,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>73168</t>
+          <t>25120</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Chaparral</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -2714,17 +2714,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -2732,17 +2732,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>50318</t>
+          <t>73168</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Guamal</t>
+          <t>Chaparral</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -2767,17 +2767,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>50006</t>
+          <t>50318</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Acacías</t>
+          <t>Guamal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2799,11 +2799,11 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -2820,17 +2820,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -2838,17 +2838,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>25649</t>
+          <t>76834</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Valle del Cauca</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>73622</t>
+          <t>50006</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Roncesvalles</t>
+          <t>Acacías</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Gutiérrez</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2958,11 +2958,11 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -2979,17 +2979,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2997,17 +2997,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>63302</t>
+          <t>73622</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Génova</t>
+          <t>Roncesvalles</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Quindío</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -3032,17 +3032,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -3050,12 +3050,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>25053</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Bogotá, D.C.</t>
+          <t>Arbeláez</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3064,11 +3064,11 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -3085,17 +3085,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -3103,25 +3103,25 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20001</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Valledupar</t>
+          <t>Gutiérrez</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Cesar</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -3138,17 +3138,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -3156,17 +3156,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>47053</t>
+          <t>63302</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Aracataca</t>
+          <t>Génova</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Quindío</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-01 19:00</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-01 07:00</t>
+          <t>2026-08-02 07:00</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3209,17 +3209,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>47001</t>
+          <t>25535</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Santa Marta</t>
+          <t>Pasca</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -3262,17 +3262,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>52560</t>
+          <t>76736</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Valle del Cauca</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -3315,17 +3315,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>52215</t>
+          <t>25845</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Une</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -3368,17 +3368,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>52356</t>
+          <t>25178</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Ipiales</t>
+          <t>Chipaque</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>52224</t>
+          <t>25754</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Cuaspud</t>
+          <t>Soacha</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -3474,17 +3474,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>52573</t>
+          <t>73001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Puerres</t>
+          <t>Ibagué</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -3527,17 +3527,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>52022</t>
+          <t>63690</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Aldana</t>
+          <t>Salento</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Quindío</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -3580,17 +3580,17 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>73043</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Pupiales</t>
+          <t>Anzoátegui</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -3633,25 +3633,25 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>52317</t>
+          <t>73686</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Guachucal</t>
+          <t>Santa Isabel</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -3686,17 +3686,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>52287</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Funes</t>
+          <t>La Calera</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -3739,17 +3739,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>52227</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Cumbal</t>
+          <t>Bogotá, D.C.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -3792,17 +3792,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>66001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Sapuyes</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -3845,25 +3845,25 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>52788</t>
+          <t>73461</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tangua</t>
+          <t>Murillo</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -3898,17 +3898,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>52838</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Túquerres</t>
+          <t>Guasca</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>52001</t>
+          <t>66682</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Pasto</t>
+          <t>Santa Rosa De Cabal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -4004,25 +4004,25 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>52435</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Mallama</t>
+          <t>Villamaria</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -4057,17 +4057,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>52378</t>
+          <t>73870</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>La Cruz</t>
+          <t>Villahermosa</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -4110,17 +4110,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>19701</t>
+          <t>73152</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Santa Rosa</t>
+          <t>Casabianca</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -4163,17 +4163,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>San Sebastián</t>
+          <t>Manizales</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -4216,17 +4216,17 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>19397</t>
+          <t>73347</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>La Vega</t>
+          <t>Herveo</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -4269,17 +4269,17 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>41668</t>
+          <t>15822</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>San Agustín</t>
+          <t>Tota</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -4322,17 +4322,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>15226</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Saladoblanco</t>
+          <t>Cuítiva</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -4375,17 +4375,17 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>41359</t>
+          <t>15047</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Isnos</t>
+          <t>Aquitania</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>41378</t>
+          <t>15542</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>La Argentina</t>
+          <t>Pesca</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>00000</t>
+          <t>15362</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Area En Litigio Cauca - Huila</t>
+          <t>Iza</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -4534,17 +4534,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>19760</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sotará</t>
+          <t>Toca</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -4587,17 +4587,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>19585</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Puracé</t>
+          <t>Monguí</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -4640,17 +4640,17 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>19824</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Totoró</t>
+          <t>Sogamoso</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -4693,17 +4693,17 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>15464</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Inzá</t>
+          <t>Mongua</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J81" t="n">
@@ -4746,17 +4746,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>15820</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Silvia</t>
+          <t>Tópaga</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J82" t="n">
@@ -4799,25 +4799,25 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>41801</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Teruel</t>
+          <t>Gámeza</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -4852,25 +4852,25 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>19517</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Páez</t>
+          <t>Corrales</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -4905,25 +4905,25 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>19821</t>
+          <t>15790</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Toribío</t>
+          <t>Tasco</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -4958,17 +4958,17 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>19212</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Corinto</t>
+          <t>Cerinza</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -5011,25 +5011,25 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>73555</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Planadas</t>
+          <t>Santa Rosa De Viterbo</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -5064,17 +5064,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>73616</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Rioblanco</t>
+          <t>Duitama</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -5117,17 +5117,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>50370</t>
+          <t>15757</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Uribe</t>
+          <t>Socha</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -5170,17 +5170,17 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>50400</t>
+          <t>15087</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Lejanías</t>
+          <t>Belén</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>41206</t>
+          <t>15537</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Paz De Rio</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J91" t="n">
@@ -5276,17 +5276,17 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>76111</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Socotá</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -5329,25 +5329,25 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>50223</t>
+          <t>15839</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Cubarral</t>
+          <t>Tutazá</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>25120</t>
+          <t>68264</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Encino</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -5435,17 +5435,17 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>73168</t>
+          <t>15368</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Chaparral</t>
+          <t>Jericó</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -5488,25 +5488,25 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>50318</t>
+          <t>15183</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Guamal</t>
+          <t>Chita</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -5541,25 +5541,25 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>76834</t>
+          <t>85136</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>La Salina</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Casanare</t>
         </is>
       </c>
       <c r="J97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -5594,17 +5594,17 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>50006</t>
+          <t>68217</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Acacías</t>
+          <t>Coromoro</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J98" t="n">
@@ -5647,17 +5647,17 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>25649</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>El Cocuy</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -5700,17 +5700,17 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>73622</t>
+          <t>15673</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Roncesvalles</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J100" t="n">
@@ -5753,17 +5753,17 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>25053</t>
+          <t>15317</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Arbeláez</t>
+          <t>Guacamayas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -5806,25 +5806,25 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Gutiérrez</t>
+          <t>Panqueba</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -5859,17 +5859,17 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>63302</t>
+          <t>68502</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Génova</t>
+          <t>Onzaga</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Quindío</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J103" t="n">
@@ -5912,17 +5912,17 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Pasca</t>
+          <t>El Espino</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -5965,25 +5965,25 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>76736</t>
+          <t>81794</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Tame</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Arauca</t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -6018,17 +6018,17 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>25845</t>
+          <t>68152</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Une</t>
+          <t>Carcasí</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J106" t="n">
@@ -6071,25 +6071,25 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>25178</t>
+          <t>15332</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Chipaque</t>
+          <t>Güicán De La Sierra</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -6124,25 +6124,25 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>25754</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Soacha</t>
+          <t>Chiscas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -6177,17 +6177,17 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>25279</t>
+          <t>81300</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Fómeque</t>
+          <t>Fortul</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Arauca</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -6230,17 +6230,17 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>73001</t>
+          <t>68207</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Ibagué</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -6265,17 +6265,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -6283,17 +6283,17 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>63690</t>
+          <t>52560</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Salento</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Quindío</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -6318,17 +6318,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -6336,17 +6336,17 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>73043</t>
+          <t>52356</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Anzoátegui</t>
+          <t>Ipiales</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -6371,17 +6371,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -6389,17 +6389,17 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>52224</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Santa Isabel</t>
+          <t>Cuaspud</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -6424,17 +6424,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -6442,17 +6442,17 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>52573</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>La Calera</t>
+          <t>Puerres</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -6477,17 +6477,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -6495,25 +6495,25 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>52022</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Bogotá, D.C.</t>
+          <t>Aldana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -6530,17 +6530,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -6548,17 +6548,17 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>52585</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Junín</t>
+          <t>Pupiales</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>66001</t>
+          <t>52317</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Guachucal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -6654,17 +6654,17 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>73461</t>
+          <t>52287</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Murillo</t>
+          <t>Funes</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -6689,17 +6689,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -6707,25 +6707,25 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>52227</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Guasca</t>
+          <t>Cumbal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -6742,17 +6742,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -6760,17 +6760,17 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>66682</t>
+          <t>52720</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Santa Rosa De Cabal</t>
+          <t>Sapuyes</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -6795,17 +6795,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -6813,17 +6813,17 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>52838</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Villamaria</t>
+          <t>Túquerres</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -6848,17 +6848,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -6866,17 +6866,17 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>73870</t>
+          <t>52001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Villahermosa</t>
+          <t>Pasto</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -6919,17 +6919,17 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>73152</t>
+          <t>52435</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Casabianca</t>
+          <t>Mallama</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J123" t="n">
@@ -6954,17 +6954,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -6972,17 +6972,17 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>25899</t>
+          <t>52378</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Zipaquirá</t>
+          <t>La Cruz</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -7007,17 +7007,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -7025,17 +7025,17 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>73347</t>
+          <t>19701</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Herveo</t>
+          <t>Santa Rosa</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -7060,17 +7060,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -7078,17 +7078,17 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>25200</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Cogua</t>
+          <t>San Sebastián</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -7113,17 +7113,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -7131,17 +7131,17 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>25793</t>
+          <t>41668</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Tausa</t>
+          <t>San Agustín</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J127" t="n">
@@ -7166,17 +7166,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -7184,17 +7184,17 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>25873</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Villapinzón</t>
+          <t>Saladoblanco</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J128" t="n">
@@ -7219,17 +7219,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -7237,17 +7237,17 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>25407</t>
+          <t>41359</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Lenguazaque</t>
+          <t>Isnos</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J129" t="n">
@@ -7272,17 +7272,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -7290,17 +7290,17 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>25317</t>
+          <t>41378</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Guachetá</t>
+          <t>La Argentina</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J130" t="n">
@@ -7325,17 +7325,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -7343,17 +7343,17 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>00000</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Ventaquemada</t>
+          <t>Area En Litigio Cauca - Huila</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J131" t="n">
@@ -7378,17 +7378,17 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -7396,17 +7396,17 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>19585</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Tota</t>
+          <t>Puracé</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J132" t="n">
@@ -7431,17 +7431,17 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -7449,17 +7449,17 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>15226</t>
+          <t>19824</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Cuítiva</t>
+          <t>Totoró</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -7484,17 +7484,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -7502,17 +7502,17 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>19355</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Aquitania</t>
+          <t>Inzá</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -7537,17 +7537,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -7555,17 +7555,17 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>15362</t>
+          <t>19743</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Iza</t>
+          <t>Silvia</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J135" t="n">
@@ -7590,17 +7590,17 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -7608,25 +7608,25 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>15466</t>
+          <t>41801</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Monguí</t>
+          <t>Teruel</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -7643,17 +7643,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -7661,17 +7661,17 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>15759</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Sogamoso</t>
+          <t>Jambaló</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -7696,17 +7696,17 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -7714,25 +7714,25 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>19517</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Mongua</t>
+          <t>Páez</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J138" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -7749,17 +7749,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -7767,25 +7767,25 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>15820</t>
+          <t>19821</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Tópaga</t>
+          <t>Toribío</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -7802,17 +7802,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -7820,25 +7820,25 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>15296</t>
+          <t>19212</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Gámeza</t>
+          <t>Corinto</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -7855,17 +7855,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>15215</t>
+          <t>19455</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Corrales</t>
+          <t>Miranda</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J141" t="n">
@@ -7908,17 +7908,17 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -7926,25 +7926,25 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>15790</t>
+          <t>73555</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Tasco</t>
+          <t>Planadas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -7961,17 +7961,17 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -7979,17 +7979,17 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>76275</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Cerinza</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Valle del Cauca</t>
         </is>
       </c>
       <c r="J143" t="n">
@@ -8014,17 +8014,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -8032,25 +8032,25 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>73616</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Santa Rosa De Viterbo</t>
+          <t>Rioblanco</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -8067,17 +8067,17 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -8085,17 +8085,17 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>50370</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Duitama</t>
+          <t>Uribe</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J145" t="n">
@@ -8120,17 +8120,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -8138,17 +8138,17 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>15757</t>
+          <t>50400</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Socha</t>
+          <t>Lejanías</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J146" t="n">
@@ -8173,17 +8173,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -8191,17 +8191,17 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>15087</t>
+          <t>41206</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Belén</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J147" t="n">
@@ -8226,17 +8226,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -8244,25 +8244,25 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>76111</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Socotá</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Valle del Cauca</t>
         </is>
       </c>
       <c r="J148" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -8279,17 +8279,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -8297,25 +8297,25 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>50223</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Tutazá</t>
+          <t>Cubarral</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J149" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -8332,17 +8332,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -8350,17 +8350,17 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>68264</t>
+          <t>25120</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Encino</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J150" t="n">
@@ -8385,17 +8385,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -8403,25 +8403,25 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>15368</t>
+          <t>73168</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Jericó</t>
+          <t>Chaparral</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J151" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -8438,17 +8438,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -8456,25 +8456,25 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>15183</t>
+          <t>50318</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Chita</t>
+          <t>Guamal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J152" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -8491,17 +8491,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -8509,25 +8509,25 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>85136</t>
+          <t>76834</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>La Salina</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Casanare</t>
+          <t>Valle del Cauca</t>
         </is>
       </c>
       <c r="J153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -8544,17 +8544,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -8562,17 +8562,17 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>68217</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Coromoro</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J154" t="n">
@@ -8597,17 +8597,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -8615,25 +8615,25 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>73622</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>El Cocuy</t>
+          <t>Roncesvalles</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -8650,17 +8650,17 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -8668,17 +8668,17 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>15673</t>
+          <t>25053</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Arbeláez</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -8703,17 +8703,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -8721,25 +8721,25 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>15317</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Guacamayas</t>
+          <t>Gutiérrez</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J157" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -8756,17 +8756,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -8774,17 +8774,17 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>15522</t>
+          <t>63302</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Panqueba</t>
+          <t>Génova</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Quindío</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -8809,17 +8809,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -8827,17 +8827,17 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>68502</t>
+          <t>73624</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Onzaga</t>
+          <t>Rovira</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -8862,17 +8862,17 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -8880,17 +8880,17 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>15248</t>
+          <t>63548</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>El Espino</t>
+          <t>Pijao</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Quindío</t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -8933,25 +8933,25 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>81794</t>
+          <t>25535</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Tame</t>
+          <t>Pasca</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Arauca</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J161" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -8968,17 +8968,17 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -8986,25 +8986,25 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>15332</t>
+          <t>76736</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Güicán De La Sierra</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Valle del Cauca</t>
         </is>
       </c>
       <c r="J162" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -9021,17 +9021,17 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -9039,25 +9039,25 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>15180</t>
+          <t>25845</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Chiscas</t>
+          <t>Une</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J163" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -9074,17 +9074,17 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>20001</t>
+          <t>25178</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Valledupar</t>
+          <t>Chipaque</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Cesar</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -9127,17 +9127,17 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -9145,17 +9145,17 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>47053</t>
+          <t>73124</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Aracataca</t>
+          <t>Cajamarca</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -9180,17 +9180,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-08-01 19:00</t>
+          <t>2026-08-02 19:00</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-08-02 07:00</t>
+          <t>2026-08-03 07:00</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -9198,17 +9198,17 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>47001</t>
+          <t>25754</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Santa Marta</t>
+          <t>Soacha</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -9251,17 +9251,17 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>52560</t>
+          <t>25279</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Fómeque</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -9304,17 +9304,17 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>52356</t>
+          <t>73001</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Ipiales</t>
+          <t>Ibagué</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -9357,17 +9357,17 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>52224</t>
+          <t>63690</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Cuaspud</t>
+          <t>Salento</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Quindío</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -9410,17 +9410,17 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>52022</t>
+          <t>73043</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Aldana</t>
+          <t>Anzoátegui</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -9463,25 +9463,25 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>73686</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Pupiales</t>
+          <t>Santa Isabel</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J171" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -9516,17 +9516,17 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>52317</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Guachucal</t>
+          <t>La Calera</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J172" t="n">
@@ -9569,17 +9569,17 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>52227</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Cumbal</t>
+          <t>Bogotá, D.C.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J173" t="n">
@@ -9622,17 +9622,17 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>25372</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Sapuyes</t>
+          <t>Junín</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J174" t="n">
@@ -9675,17 +9675,17 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>86760</t>
+          <t>66001</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Putumayo</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="J175" t="n">
@@ -9728,25 +9728,25 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>52838</t>
+          <t>73461</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Túquerres</t>
+          <t>Murillo</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J176" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -9781,17 +9781,17 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>52001</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Pasto</t>
+          <t>Guasca</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J177" t="n">
@@ -9834,17 +9834,17 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>52435</t>
+          <t>66682</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Mallama</t>
+          <t>Santa Rosa De Cabal</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="J178" t="n">
@@ -9887,25 +9887,25 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>52110</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Buesaco</t>
+          <t>Villamaria</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="J179" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -9940,25 +9940,25 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>52699</t>
+          <t>73870</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Villahermosa</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J180" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -9993,25 +9993,25 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>52378</t>
+          <t>73152</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>La Cruz</t>
+          <t>Casabianca</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J181" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -10046,17 +10046,17 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>19701</t>
+          <t>25899</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Santa Rosa</t>
+          <t>Zipaquirá</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J182" t="n">
@@ -10099,25 +10099,25 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>San Sebastián</t>
+          <t>Manizales</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="J183" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -10152,25 +10152,25 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>41668</t>
+          <t>73347</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>San Agustín</t>
+          <t>Herveo</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J184" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -10205,17 +10205,17 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Saladoblanco</t>
+          <t>Cogua</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J185" t="n">
@@ -10258,17 +10258,17 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>41359</t>
+          <t>25793</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Isnos</t>
+          <t>Tausa</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J186" t="n">
@@ -10311,17 +10311,17 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>41378</t>
+          <t>17486</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>La Argentina</t>
+          <t>Neira</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="J187" t="n">
@@ -10364,17 +10364,17 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>00000</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Area En Litigio Cauca - Huila</t>
+          <t>Marulanda</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="J188" t="n">
@@ -10417,17 +10417,17 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>19760</t>
+          <t>25653</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Sotará</t>
+          <t>San Cayetano</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J189" t="n">
@@ -10470,17 +10470,17 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>19585</t>
+          <t>25154</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Puracé</t>
+          <t>Carmen De Carupa</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J190" t="n">
@@ -10523,17 +10523,17 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>19824</t>
+          <t>15822</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Totoró</t>
+          <t>Tota</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J191" t="n">
@@ -10576,17 +10576,17 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>15047</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Inzá</t>
+          <t>Aquitania</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J192" t="n">
@@ -10629,17 +10629,17 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Silvia</t>
+          <t>Monguí</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J193" t="n">
@@ -10682,17 +10682,17 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>41801</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Teruel</t>
+          <t>Sogamoso</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J194" t="n">
@@ -10735,25 +10735,25 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>19517</t>
+          <t>15464</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Páez</t>
+          <t>Mongua</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J195" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -10788,25 +10788,25 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>19821</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Toribío</t>
+          <t>Gámeza</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J196" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -10841,25 +10841,25 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>19212</t>
+          <t>15790</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Corinto</t>
+          <t>Tasco</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J197" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -10894,25 +10894,25 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>73555</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Planadas</t>
+          <t>Cerinza</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J198" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -10947,25 +10947,25 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>73616</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Rioblanco</t>
+          <t>Santa Rosa De Viterbo</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J199" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -11000,17 +11000,17 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>50370</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Uribe</t>
+          <t>Duitama</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J200" t="n">
@@ -11053,17 +11053,17 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>50400</t>
+          <t>15757</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Lejanías</t>
+          <t>Socha</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J201" t="n">
@@ -11106,17 +11106,17 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>41206</t>
+          <t>15087</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Belén</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J202" t="n">
@@ -11159,25 +11159,25 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>76111</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Socotá</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J203" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -11212,17 +11212,17 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>50223</t>
+          <t>15839</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Cubarral</t>
+          <t>Tutazá</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J204" t="n">
@@ -11265,17 +11265,17 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>25120</t>
+          <t>68264</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Encino</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J205" t="n">
@@ -11318,25 +11318,25 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>73168</t>
+          <t>15183</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Chaparral</t>
+          <t>Chita</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J206" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -11371,17 +11371,17 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>50318</t>
+          <t>85136</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Guamal</t>
+          <t>La Salina</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Casanare</t>
         </is>
       </c>
       <c r="J207" t="n">
@@ -11424,17 +11424,17 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>76834</t>
+          <t>68217</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>Coromoro</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J208" t="n">
@@ -11477,25 +11477,25 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>25649</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>El Cocuy</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J209" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -11530,17 +11530,17 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>73622</t>
+          <t>15673</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Roncesvalles</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J210" t="n">
@@ -11583,17 +11583,17 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>25053</t>
+          <t>15317</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Arbeláez</t>
+          <t>Guacamayas</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J211" t="n">
@@ -11636,17 +11636,17 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Gutiérrez</t>
+          <t>Panqueba</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J212" t="n">
@@ -11689,17 +11689,17 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>63302</t>
+          <t>68502</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Génova</t>
+          <t>Onzaga</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Quindío</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J213" t="n">
@@ -11742,17 +11742,17 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>73624</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Rovira</t>
+          <t>El Espino</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J214" t="n">
@@ -11795,25 +11795,25 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>63548</t>
+          <t>81794</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Pijao</t>
+          <t>Tame</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Quindío</t>
+          <t>Arauca</t>
         </is>
       </c>
       <c r="J215" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -11848,17 +11848,17 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>68152</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Pasca</t>
+          <t>Carcasí</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J216" t="n">
@@ -11901,25 +11901,25 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>76736</t>
+          <t>15332</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Güicán De La Sierra</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J217" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -11954,25 +11954,25 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>25845</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Une</t>
+          <t>Chiscas</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J218" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -12007,17 +12007,17 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>25178</t>
+          <t>81300</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Chipaque</t>
+          <t>Fortul</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Arauca</t>
         </is>
       </c>
       <c r="J219" t="n">
@@ -12060,17 +12060,17 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>73124</t>
+          <t>68207</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Cajamarca</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J220" t="n">
@@ -12113,17 +12113,17 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>25279</t>
+          <t>68318</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Fómeque</t>
+          <t>Guaca</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J221" t="n">
@@ -12166,17 +12166,17 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>73001</t>
+          <t>68705</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Ibagué</t>
+          <t>Santa Bárbara</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J222" t="n">
@@ -12219,17 +12219,17 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>63690</t>
+          <t>68820</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Salento</t>
+          <t>Tona</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Quindío</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J223" t="n">
@@ -12272,17 +12272,17 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>73043</t>
+          <t>54174</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Anzoátegui</t>
+          <t>Chitagá</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Norte de Santander</t>
         </is>
       </c>
       <c r="J224" t="n">
@@ -12325,25 +12325,25 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>54743</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Santa Isabel</t>
+          <t>Silos</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Norte de Santander</t>
         </is>
       </c>
       <c r="J225" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -12378,17 +12378,17 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>54480</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>La Calera</t>
+          <t>Mutiscua</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Norte de Santander</t>
         </is>
       </c>
       <c r="J226" t="n">
@@ -12431,25 +12431,25 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>68867</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Bogotá, D.C.</t>
+          <t>Vetas</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J227" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -12466,17 +12466,17 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F228" t="n">
@@ -12484,25 +12484,25 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>52356</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Junín</t>
+          <t>Ipiales</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -12519,17 +12519,17 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F229" t="n">
@@ -12537,25 +12537,25 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>66001</t>
+          <t>52022</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Aldana</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J229" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -12572,17 +12572,17 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F230" t="n">
@@ -12590,25 +12590,25 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>73461</t>
+          <t>52585</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Murillo</t>
+          <t>Pupiales</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J230" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -12625,17 +12625,17 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F231" t="n">
@@ -12643,17 +12643,17 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>52317</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Guasca</t>
+          <t>Guachucal</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J231" t="n">
@@ -12678,17 +12678,17 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F232" t="n">
@@ -12696,17 +12696,17 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>66682</t>
+          <t>52227</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Santa Rosa De Cabal</t>
+          <t>Cumbal</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Risaralda</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J232" t="n">
@@ -12731,17 +12731,17 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F233" t="n">
@@ -12749,25 +12749,25 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>52720</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Villamaria</t>
+          <t>Sapuyes</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J233" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -12784,17 +12784,17 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F234" t="n">
@@ -12802,25 +12802,25 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>73870</t>
+          <t>52838</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Villahermosa</t>
+          <t>Túquerres</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J234" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -12837,17 +12837,17 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F235" t="n">
@@ -12855,25 +12855,25 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>73152</t>
+          <t>52001</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Casabianca</t>
+          <t>Pasto</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J235" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -12890,17 +12890,17 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F236" t="n">
@@ -12908,17 +12908,17 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>25899</t>
+          <t>52435</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Zipaquirá</t>
+          <t>Mallama</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J236" t="n">
@@ -12943,17 +12943,17 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F237" t="n">
@@ -12961,17 +12961,17 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Manizales</t>
+          <t>Saladoblanco</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J237" t="n">
@@ -12996,17 +12996,17 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F238" t="n">
@@ -13014,25 +13014,25 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>73347</t>
+          <t>41359</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Herveo</t>
+          <t>Isnos</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J238" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -13049,17 +13049,17 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F239" t="n">
@@ -13067,17 +13067,17 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>25200</t>
+          <t>00000</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Cogua</t>
+          <t>Area En Litigio Cauca - Huila</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J239" t="n">
@@ -13102,17 +13102,17 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F240" t="n">
@@ -13120,17 +13120,17 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>25793</t>
+          <t>19585</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Tausa</t>
+          <t>Puracé</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J240" t="n">
@@ -13155,17 +13155,17 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F241" t="n">
@@ -13173,17 +13173,17 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>25873</t>
+          <t>73616</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Villapinzón</t>
+          <t>Rioblanco</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J241" t="n">
@@ -13208,17 +13208,17 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F242" t="n">
@@ -13226,17 +13226,17 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>25407</t>
+          <t>50370</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Lenguazaque</t>
+          <t>Uribe</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J242" t="n">
@@ -13261,17 +13261,17 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F243" t="n">
@@ -13279,17 +13279,17 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>25317</t>
+          <t>50223</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Guachetá</t>
+          <t>Cubarral</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J243" t="n">
@@ -13314,17 +13314,17 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F244" t="n">
@@ -13332,17 +13332,17 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>73168</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Ventaquemada</t>
+          <t>Chaparral</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J244" t="n">
@@ -13367,17 +13367,17 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F245" t="n">
@@ -13385,17 +13385,17 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Aquitania</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J245" t="n">
@@ -13420,17 +13420,17 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -13438,17 +13438,17 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>15466</t>
+          <t>25053</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Monguí</t>
+          <t>Arbeláez</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J246" t="n">
@@ -13473,17 +13473,17 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -13491,17 +13491,17 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>15759</t>
+          <t>25535</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Sogamoso</t>
+          <t>Pasca</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J247" t="n">
@@ -13526,17 +13526,17 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F248" t="n">
@@ -13544,17 +13544,17 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Mongua</t>
+          <t>Bogotá, D.C.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J248" t="n">
@@ -13579,17 +13579,17 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -13597,12 +13597,12 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>15820</t>
+          <t>15183</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Tópaga</t>
+          <t>Chita</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -13632,17 +13632,17 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F250" t="n">
@@ -13650,17 +13650,17 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>15296</t>
+          <t>85136</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Gámeza</t>
+          <t>La Salina</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Casanare</t>
         </is>
       </c>
       <c r="J250" t="n">
@@ -13685,17 +13685,17 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F251" t="n">
@@ -13703,12 +13703,12 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>15215</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Corrales</t>
+          <t>El Cocuy</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -13738,17 +13738,17 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -13756,25 +13756,25 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>15790</t>
+          <t>81794</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Tasco</t>
+          <t>Tame</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Arauca</t>
         </is>
       </c>
       <c r="J252" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -13791,17 +13791,17 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F253" t="n">
@@ -13809,12 +13809,12 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>15332</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Cerinza</t>
+          <t>Güicán De La Sierra</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -13823,11 +13823,11 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -13844,17 +13844,17 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -13862,12 +13862,12 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Santa Rosa De Viterbo</t>
+          <t>Chiscas</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -13897,17 +13897,17 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F255" t="n">
@@ -13915,17 +13915,17 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>68318</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Duitama</t>
+          <t>Guaca</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J255" t="n">
@@ -13950,17 +13950,17 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F256" t="n">
@@ -13968,17 +13968,17 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>15757</t>
+          <t>68705</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Socha</t>
+          <t>Santa Bárbara</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J256" t="n">
@@ -14003,17 +14003,17 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F257" t="n">
@@ -14021,17 +14021,17 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>15087</t>
+          <t>54174</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Belén</t>
+          <t>Chitagá</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Norte de Santander</t>
         </is>
       </c>
       <c r="J257" t="n">
@@ -14056,17 +14056,17 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00</t>
+          <t>2026-08-03 19:00</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-08-03 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="F258" t="n">
@@ -14074,1348 +14074,23 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>54743</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Socotá</t>
+          <t>Silos</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Norte de Santander</t>
         </is>
       </c>
       <c r="J258" t="n">
         <v>3</v>
       </c>
       <c r="K258" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F259" t="n">
-        <v>12</v>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>15839</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Tutazá</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J259" t="n">
-        <v>3</v>
-      </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F260" t="n">
-        <v>12</v>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>68264</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>Encino</t>
-        </is>
-      </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="J260" t="n">
-        <v>3</v>
-      </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F261" t="n">
-        <v>12</v>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>15183</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>Chita</t>
-        </is>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J261" t="n">
-        <v>3</v>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F262" t="n">
-        <v>12</v>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>85136</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>La Salina</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>Casanare</t>
-        </is>
-      </c>
-      <c r="J262" t="n">
-        <v>3</v>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F263" t="n">
-        <v>12</v>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>68217</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>Coromoro</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="J263" t="n">
-        <v>3</v>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F264" t="n">
-        <v>12</v>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>15244</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>El Cocuy</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J264" t="n">
-        <v>3</v>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F265" t="n">
-        <v>12</v>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>15673</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>San Mateo</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J265" t="n">
-        <v>3</v>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F266" t="n">
-        <v>12</v>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>15317</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>Guacamayas</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J266" t="n">
-        <v>3</v>
-      </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F267" t="n">
-        <v>12</v>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>15522</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>Panqueba</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J267" t="n">
-        <v>3</v>
-      </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F268" t="n">
-        <v>12</v>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>68502</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>Onzaga</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="J268" t="n">
-        <v>3</v>
-      </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F269" t="n">
-        <v>12</v>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>15248</t>
-        </is>
-      </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>El Espino</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J269" t="n">
-        <v>3</v>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F270" t="n">
-        <v>12</v>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>81794</t>
-        </is>
-      </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>Tame</t>
-        </is>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="J270" t="n">
-        <v>3</v>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F271" t="n">
-        <v>12</v>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>68152</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>Carcasí</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="J271" t="n">
-        <v>3</v>
-      </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F272" t="n">
-        <v>12</v>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>15332</t>
-        </is>
-      </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>Güicán De La Sierra</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J272" t="n">
-        <v>3</v>
-      </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F273" t="n">
-        <v>12</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>15180</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>Chiscas</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J273" t="n">
-        <v>3</v>
-      </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F274" t="n">
-        <v>12</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>68207</t>
-        </is>
-      </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>Concepción</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="J274" t="n">
-        <v>3</v>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F275" t="n">
-        <v>12</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>68669</t>
-        </is>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>San Andrés</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="J275" t="n">
-        <v>3</v>
-      </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F276" t="n">
-        <v>12</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>68162</t>
-        </is>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>Cerrito</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="J276" t="n">
-        <v>3</v>
-      </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F277" t="n">
-        <v>12</v>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>68318</t>
-        </is>
-      </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>Guaca</t>
-        </is>
-      </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="J277" t="n">
-        <v>3</v>
-      </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F278" t="n">
-        <v>12</v>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>68705</t>
-        </is>
-      </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>Santa Bárbara</t>
-        </is>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="J278" t="n">
-        <v>3</v>
-      </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F279" t="n">
-        <v>12</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>68820</t>
-        </is>
-      </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>Tona</t>
-        </is>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="J279" t="n">
-        <v>3</v>
-      </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F280" t="n">
-        <v>12</v>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>54174</t>
-        </is>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>Chitagá</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>Norte de Santander</t>
-        </is>
-      </c>
-      <c r="J280" t="n">
-        <v>3</v>
-      </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F281" t="n">
-        <v>12</v>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>54743</t>
-        </is>
-      </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>Silos</t>
-        </is>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>Norte de Santander</t>
-        </is>
-      </c>
-      <c r="J281" t="n">
-        <v>3</v>
-      </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F282" t="n">
-        <v>12</v>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>54480</t>
-        </is>
-      </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>Mutiscua</t>
-        </is>
-      </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t>Norte de Santander</t>
-        </is>
-      </c>
-      <c r="J282" t="n">
-        <v>3</v>
-      </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>2026-08-02 19:00</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>2026-08-03 07:00</t>
-        </is>
-      </c>
-      <c r="F283" t="n">
-        <v>12</v>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>68867</t>
-        </is>
-      </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>Vetas</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>Santander</t>
-        </is>
-      </c>
-      <c r="J283" t="n">
-        <v>3</v>
-      </c>
-      <c r="K283" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
